--- a/E_laberintodeltesoro/graficas.xlsx
+++ b/E_laberintodeltesoro/graficas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\posgrado\analisis_algoritmos\laberintodeltesoro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\posgrado\analisis_algoritmos\E_laberintodeltesoro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25DB788A-C8EF-4011-A77C-DCA3DBC210AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF74581-C544-4A0F-B711-75657B85FCE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pasos (laberinto)" sheetId="1" r:id="rId1"/>
@@ -8623,13 +8623,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:V40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B1" s="4" t="s">
         <v>4</v>
       </c>
@@ -8637,7 +8637,7 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -8651,7 +8651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>18</v>
       </c>
@@ -8665,7 +8665,7 @@
         <v>22.681999999999999</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>16</v>
       </c>
@@ -8679,7 +8679,7 @@
         <v>1.486</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>14</v>
       </c>
@@ -8693,7 +8693,7 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>12</v>
       </c>
@@ -8707,7 +8707,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>10</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>8</v>
       </c>
@@ -8735,7 +8735,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>6</v>
       </c>
@@ -8749,7 +8749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>4</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>2</v>
       </c>
@@ -8777,10 +8777,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.3">
       <c r="V14" s="3"/>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>5</v>
       </c>
@@ -8788,7 +8788,7 @@
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>22</v>
       </c>
@@ -8802,7 +8802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>20</v>
       </c>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>18</v>
       </c>
@@ -8830,7 +8830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>16</v>
       </c>
@@ -8844,7 +8844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>14</v>
       </c>
@@ -8858,7 +8858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>12</v>
       </c>
@@ -8872,7 +8872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>10</v>
       </c>
@@ -8886,7 +8886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>8</v>
       </c>
@@ -8900,7 +8900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>6</v>
       </c>
@@ -8914,7 +8914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>4</v>
       </c>
@@ -8928,7 +8928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>2</v>
       </c>
@@ -8942,7 +8942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>6</v>
       </c>
@@ -8950,7 +8950,7 @@
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>20</v>
       </c>
@@ -8964,7 +8964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>18</v>
       </c>
@@ -8978,7 +8978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>16</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>14</v>
       </c>
@@ -9006,7 +9006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>12</v>
       </c>
@@ -9020,7 +9020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>10</v>
       </c>
@@ -9034,7 +9034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>8</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>6</v>
       </c>
@@ -9062,7 +9062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>4</v>
       </c>
@@ -9076,7 +9076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>2</v>
       </c>
@@ -9105,13 +9105,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A55921A-9DA7-40EB-867B-7FD1660B5E26}">
   <dimension ref="B1:AC66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B1" s="4" t="s">
         <v>4</v>
       </c>
@@ -9119,7 +9119,7 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:29" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:29" ht="18" x14ac:dyDescent="0.35">
       <c r="B3">
         <v>18</v>
       </c>
@@ -9152,7 +9152,7 @@
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
     </row>
-    <row r="4" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>16</v>
       </c>
@@ -9166,7 +9166,7 @@
         <v>1.486</v>
       </c>
     </row>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>14</v>
       </c>
@@ -9180,7 +9180,7 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="6" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>12</v>
       </c>
@@ -9194,7 +9194,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>10</v>
       </c>
@@ -9208,7 +9208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>8</v>
       </c>
@@ -9222,7 +9222,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="9" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>6</v>
       </c>
@@ -9236,7 +9236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>4</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>2</v>
       </c>
@@ -9264,10 +9264,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:29" x14ac:dyDescent="0.3">
       <c r="V14" s="3"/>
     </row>
-    <row r="15" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>5</v>
       </c>
@@ -9275,7 +9275,7 @@
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>5000</v>
       </c>
@@ -9295,7 +9295,7 @@
       <c r="AB16" s="4"/>
       <c r="AC16" s="4"/>
     </row>
-    <row r="17" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>4900</v>
       </c>
@@ -9321,7 +9321,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="18" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>4800</v>
       </c>
@@ -9347,7 +9347,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>4700</v>
       </c>
@@ -9373,7 +9373,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="20" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>4600</v>
       </c>
@@ -9399,7 +9399,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="21" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>4500</v>
       </c>
@@ -9425,7 +9425,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="22" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>4400</v>
       </c>
@@ -9451,7 +9451,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>4300</v>
       </c>
@@ -9477,7 +9477,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="24" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>4200</v>
       </c>
@@ -9503,7 +9503,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="25" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>4100</v>
       </c>
@@ -9529,7 +9529,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="26" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>4000</v>
       </c>
@@ -9555,7 +9555,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="27" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>3900</v>
       </c>
@@ -9581,7 +9581,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>3800</v>
       </c>
@@ -9607,7 +9607,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="29" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>3700</v>
       </c>
@@ -9633,7 +9633,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="30" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>3600</v>
       </c>
@@ -9659,7 +9659,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="31" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>3500</v>
       </c>
@@ -9685,7 +9685,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>3400</v>
       </c>
@@ -9711,7 +9711,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>3300</v>
       </c>
@@ -9737,7 +9737,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>3200</v>
       </c>
@@ -9763,7 +9763,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>3100</v>
       </c>
@@ -9789,7 +9789,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>3000</v>
       </c>
@@ -9815,7 +9815,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>2900</v>
       </c>
@@ -9841,7 +9841,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>2800</v>
       </c>
@@ -9867,7 +9867,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>2700</v>
       </c>
@@ -9893,7 +9893,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>2600</v>
       </c>
@@ -9919,7 +9919,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>2500</v>
       </c>
@@ -9945,7 +9945,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>2400</v>
       </c>
@@ -9971,7 +9971,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>2300</v>
       </c>
@@ -9997,7 +9997,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>2200</v>
       </c>
@@ -10023,7 +10023,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>2100</v>
       </c>
@@ -10049,7 +10049,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>2000</v>
       </c>
@@ -10075,7 +10075,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>1900</v>
       </c>
@@ -10101,7 +10101,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>1800</v>
       </c>
@@ -10128,7 +10128,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="49" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>1700</v>
       </c>
@@ -10154,7 +10154,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="50" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>1600</v>
       </c>
@@ -10180,7 +10180,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="51" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>1500</v>
       </c>
@@ -10206,7 +10206,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="52" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>1400</v>
       </c>
@@ -10232,7 +10232,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="53" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>1300</v>
       </c>
@@ -10258,7 +10258,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="54" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>1200</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="55" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>1100</v>
       </c>
@@ -10310,7 +10310,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="56" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>1000</v>
       </c>
@@ -10336,7 +10336,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="57" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>900</v>
       </c>
@@ -10362,7 +10362,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="58" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>800</v>
       </c>
@@ -10388,7 +10388,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="59" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>700</v>
       </c>
@@ -10414,7 +10414,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="60" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>600</v>
       </c>
@@ -10440,7 +10440,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="61" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>500</v>
       </c>
@@ -10466,7 +10466,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="62" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>400</v>
       </c>
@@ -10492,7 +10492,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="63" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>300</v>
       </c>
@@ -10518,7 +10518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>200</v>
       </c>
@@ -10544,7 +10544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>100</v>
       </c>
@@ -10570,7 +10570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:29" x14ac:dyDescent="0.3">
       <c r="Z66">
         <v>100</v>
       </c>
